--- a/outputs/3_effective_rates_lake_2023.xlsx
+++ b/outputs/3_effective_rates_lake_2023.xlsx
@@ -31049,7 +31049,7 @@
         <v>59267.21</v>
       </c>
       <c r="L206" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
         <v>59267.19</v>
